--- a/N100 Financial Intelligence Platform/data/raw/peer_groups.xlsx
+++ b/N100 Financial Intelligence Platform/data/raw/peer_groups.xlsx
@@ -1,63 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>group_name</t>
-  </si>
-  <si>
-    <t>sector_id</t>
-  </si>
-  <si>
-    <t>IT Large Cap</t>
-  </si>
-  <si>
-    <t>Energy Large Cap</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -65,36 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -382,35 +408,1045 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>peer_group_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>company_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>is_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Private Banks</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Private Banks</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Private Banks</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Private Banks</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Private Banks</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Public Sector Banks</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Public Sector Banks</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Public Sector Banks</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Public Sector Banks</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LTIM</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TATAMOTORS</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Life Insurance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Life Insurance</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Life Insurance</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Life Insurance</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Power &amp; Utilities</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Power &amp; Utilities</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Power &amp; Utilities</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Power &amp; Utilities</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Power &amp; Utilities</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Power &amp; Utilities</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Power &amp; Utilities</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Consumer Finance</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Consumer Finance</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Consumer Finance</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>